--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2021_antofagasta.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2021_antofagasta.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:42</t>
+    <t xml:space="preserve">2026-10-05 02:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>420351.97</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>439946.06</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>454973.09</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>463951.62</v>
+        <v>463951.63</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>335150.84</v>
@@ -1163,7 +1163,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>491440.62</v>
+        <v>491440.63</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>351817.06</v>
@@ -1196,7 +1196,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>499406.12</v>
+        <v>499406.13</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>362756.59</v>
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>518608.62</v>
+        <v>518608.63</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>372099.75</v>
@@ -1262,7 +1262,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>528693.12</v>
+        <v>528693.13</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>384571.75</v>
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>537167.62</v>
+        <v>537167.63</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>388053</v>
@@ -1287,7 +1287,7 @@
         <v>537549.38</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>572494.12</v>
+        <v>572494.13</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>403039.09</v>
@@ -1493,7 +1493,7 @@
         <v>75</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>634062.62</v>
+        <v>634062.63</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>442966.53</v>
@@ -1529,7 +1529,7 @@
         <v>627341</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>657305.81</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>709349.12</v>
+        <v>709349.13</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>497221.19</v>
